--- a/output/yearly_total_coral_cover_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_34_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26232769840163</v>
+        <v>1.26137540312851</v>
       </c>
       <c r="C3" t="n">
-        <v>4.649249731341627</v>
+        <v>4.671280149824924</v>
       </c>
       <c r="D3" t="n">
-        <v>6.190434786755509</v>
+        <v>6.041700009562117</v>
       </c>
       <c r="E3" t="n">
-        <v>12.10201221649876</v>
+        <v>11.97435556251555</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.391470146175031</v>
+        <v>1.405530998353976</v>
       </c>
       <c r="C4" t="n">
-        <v>5.228920916087104</v>
+        <v>5.224872749393521</v>
       </c>
       <c r="D4" t="n">
-        <v>6.456407742555772</v>
+        <v>6.391889855198343</v>
       </c>
       <c r="E4" t="n">
-        <v>13.07679880481791</v>
+        <v>13.02229360294584</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.561730005549174</v>
+        <v>1.593897951259009</v>
       </c>
       <c r="C5" t="n">
-        <v>5.989961699345359</v>
+        <v>5.969444001474319</v>
       </c>
       <c r="D5" t="n">
-        <v>6.819944005173372</v>
+        <v>6.75964268440672</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3716357100679</v>
+        <v>14.32298463714005</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.744369401736888</v>
+        <v>1.800455081279786</v>
       </c>
       <c r="C6" t="n">
-        <v>6.919933121840846</v>
+        <v>6.869187337916373</v>
       </c>
       <c r="D6" t="n">
-        <v>7.2879034735443</v>
+        <v>7.147270177580025</v>
       </c>
       <c r="E6" t="n">
-        <v>15.95220599712203</v>
+        <v>15.81691259677618</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.949430781094823</v>
+        <v>2.032868782630311</v>
       </c>
       <c r="C7" t="n">
-        <v>8.051231521210346</v>
+        <v>7.92756409162425</v>
       </c>
       <c r="D7" t="n">
-        <v>7.687216696347445</v>
+        <v>7.513640184461445</v>
       </c>
       <c r="E7" t="n">
-        <v>17.68787899865261</v>
+        <v>17.47407305871601</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.166554659890866</v>
+        <v>1.237669270712787</v>
       </c>
       <c r="C8" t="n">
-        <v>5.792047787576889</v>
+        <v>5.625531851514984</v>
       </c>
       <c r="D8" t="n">
-        <v>5.950359839097251</v>
+        <v>5.788625953938189</v>
       </c>
       <c r="E8" t="n">
-        <v>12.90896228656501</v>
+        <v>12.65182707616596</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.430190217645059</v>
+        <v>1.546351526064799</v>
       </c>
       <c r="C9" t="n">
-        <v>7.273288033177349</v>
+        <v>7.047776632033469</v>
       </c>
       <c r="D9" t="n">
-        <v>6.464558134589956</v>
+        <v>6.298361210147217</v>
       </c>
       <c r="E9" t="n">
-        <v>15.16803638541236</v>
+        <v>14.89248936824549</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.70039348418242</v>
+        <v>1.865460332709406</v>
       </c>
       <c r="C10" t="n">
-        <v>8.999901146789266</v>
+        <v>8.667733439449027</v>
       </c>
       <c r="D10" t="n">
-        <v>6.98851778069224</v>
+        <v>6.791072361364965</v>
       </c>
       <c r="E10" t="n">
-        <v>17.68881241166393</v>
+        <v>17.3242661335234</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954428012610404</v>
+        <v>2.177654430072039</v>
       </c>
       <c r="C11" t="n">
-        <v>10.82140372329919</v>
+        <v>10.4242519845532</v>
       </c>
       <c r="D11" t="n">
-        <v>7.468040929385001</v>
+        <v>7.264540889718717</v>
       </c>
       <c r="E11" t="n">
-        <v>20.24387266529459</v>
+        <v>19.86644730434395</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.21551242639525</v>
+        <v>2.469595766564989</v>
       </c>
       <c r="C12" t="n">
-        <v>12.67113044899579</v>
+        <v>12.24736248909871</v>
       </c>
       <c r="D12" t="n">
-        <v>7.927589620914914</v>
+        <v>7.677702246690798</v>
       </c>
       <c r="E12" t="n">
-        <v>22.81423249630596</v>
+        <v>22.39466050235449</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.451024749042707</v>
+        <v>2.747384616149802</v>
       </c>
       <c r="C13" t="n">
-        <v>14.50628411366179</v>
+        <v>14.09415693658704</v>
       </c>
       <c r="D13" t="n">
-        <v>8.352769978346311</v>
+        <v>8.06646005052019</v>
       </c>
       <c r="E13" t="n">
-        <v>25.31007884105081</v>
+        <v>24.90800160325703</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.414021035903724</v>
+        <v>1.57653955086474</v>
       </c>
       <c r="C14" t="n">
-        <v>9.972200480657401</v>
+        <v>9.764374309145394</v>
       </c>
       <c r="D14" t="n">
-        <v>6.283725268416922</v>
+        <v>6.088465467519274</v>
       </c>
       <c r="E14" t="n">
-        <v>17.66994678497804</v>
+        <v>17.42937932752941</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.42351453620379</v>
+        <v>1.60275221456813</v>
       </c>
       <c r="C15" t="n">
-        <v>10.82105881565736</v>
+        <v>10.67299162690286</v>
       </c>
       <c r="D15" t="n">
-        <v>6.27070729385861</v>
+        <v>6.045307838440584</v>
       </c>
       <c r="E15" t="n">
-        <v>18.51528064571976</v>
+        <v>18.32105167991157</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.621199253930928</v>
+        <v>1.836329628362531</v>
       </c>
       <c r="C16" t="n">
-        <v>12.7621801939712</v>
+        <v>12.72283174598499</v>
       </c>
       <c r="D16" t="n">
-        <v>6.66915941710422</v>
+        <v>6.444967511362418</v>
       </c>
       <c r="E16" t="n">
-        <v>21.05253886500635</v>
+        <v>21.00412888570994</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.283487861147068</v>
+        <v>1.457541911632985</v>
       </c>
       <c r="C17" t="n">
-        <v>11.6870879180046</v>
+        <v>11.80526088916479</v>
       </c>
       <c r="D17" t="n">
-        <v>6.148371712432415</v>
+        <v>5.93435071290661</v>
       </c>
       <c r="E17" t="n">
-        <v>19.11894749158409</v>
+        <v>19.19715351370439</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.441843765842078</v>
+        <v>1.642159567416597</v>
       </c>
       <c r="C18" t="n">
-        <v>13.63116435690822</v>
+        <v>13.88089152043748</v>
       </c>
       <c r="D18" t="n">
-        <v>6.50392146100244</v>
+        <v>6.308583120288452</v>
       </c>
       <c r="E18" t="n">
-        <v>21.57692958375274</v>
+        <v>21.83163420814253</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.428688346605171</v>
+        <v>1.626667588643583</v>
       </c>
       <c r="C19" t="n">
-        <v>14.56079107553657</v>
+        <v>14.90988092421265</v>
       </c>
       <c r="D19" t="n">
-        <v>6.558702982899411</v>
+        <v>6.343837680347955</v>
       </c>
       <c r="E19" t="n">
-        <v>22.54818240504115</v>
+        <v>22.88038619320419</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.566457001942126</v>
+        <v>1.793073824513417</v>
       </c>
       <c r="C20" t="n">
-        <v>16.64032906267216</v>
+        <v>17.09292457180699</v>
       </c>
       <c r="D20" t="n">
-        <v>6.992066054508039</v>
+        <v>6.736605484385976</v>
       </c>
       <c r="E20" t="n">
-        <v>25.19885211912233</v>
+        <v>25.62260388070638</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9195048997975628</v>
+        <v>1.056880856052819</v>
       </c>
       <c r="C21" t="n">
-        <v>12.11351985082125</v>
+        <v>12.52338969986725</v>
       </c>
       <c r="D21" t="n">
-        <v>5.806684241446355</v>
+        <v>5.583228646482739</v>
       </c>
       <c r="E21" t="n">
-        <v>18.83970899206517</v>
+        <v>19.16349920240281</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_34_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26137540312851</v>
+        <v>1.249447168521912</v>
       </c>
       <c r="C3" t="n">
-        <v>4.671280149824924</v>
+        <v>4.612502914771668</v>
       </c>
       <c r="D3" t="n">
-        <v>6.041700009562117</v>
+        <v>6.047345058861536</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97435556251555</v>
+        <v>11.90929514215512</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.405530998353976</v>
+        <v>1.368716829038843</v>
       </c>
       <c r="C4" t="n">
-        <v>5.224872749393521</v>
+        <v>5.114406160457275</v>
       </c>
       <c r="D4" t="n">
-        <v>6.391889855198343</v>
+        <v>6.315098865898177</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02229360294584</v>
+        <v>12.79822185539429</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.593897951259009</v>
+        <v>1.536481830313446</v>
       </c>
       <c r="C5" t="n">
-        <v>5.969444001474319</v>
+        <v>5.765294240591599</v>
       </c>
       <c r="D5" t="n">
-        <v>6.75964268440672</v>
+        <v>6.626333007151276</v>
       </c>
       <c r="E5" t="n">
-        <v>14.32298463714005</v>
+        <v>13.92810907805632</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.800455081279786</v>
+        <v>1.735580846326422</v>
       </c>
       <c r="C6" t="n">
-        <v>6.869187337916373</v>
+        <v>6.594201618341576</v>
       </c>
       <c r="D6" t="n">
-        <v>7.147270177580025</v>
+        <v>6.922626489598771</v>
       </c>
       <c r="E6" t="n">
-        <v>15.81691259677618</v>
+        <v>15.25240895426677</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.032868782630311</v>
+        <v>1.961589285319592</v>
       </c>
       <c r="C7" t="n">
-        <v>7.92756409162425</v>
+        <v>7.607377649546716</v>
       </c>
       <c r="D7" t="n">
-        <v>7.513640184461445</v>
+        <v>7.306787137193674</v>
       </c>
       <c r="E7" t="n">
-        <v>17.47407305871601</v>
+        <v>16.87575407205998</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.237669270712787</v>
+        <v>1.208833694622786</v>
       </c>
       <c r="C8" t="n">
-        <v>5.625531851514984</v>
+        <v>5.36156005079474</v>
       </c>
       <c r="D8" t="n">
-        <v>5.788625953938189</v>
+        <v>5.502998670771673</v>
       </c>
       <c r="E8" t="n">
-        <v>12.65182707616596</v>
+        <v>12.0733924161892</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.546351526064799</v>
+        <v>1.523677798880383</v>
       </c>
       <c r="C9" t="n">
-        <v>7.047776632033469</v>
+        <v>6.691612393393815</v>
       </c>
       <c r="D9" t="n">
-        <v>6.298361210147217</v>
+        <v>5.943081914465901</v>
       </c>
       <c r="E9" t="n">
-        <v>14.89248936824549</v>
+        <v>14.1583721067401</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.865460332709406</v>
+        <v>1.848664922423929</v>
       </c>
       <c r="C10" t="n">
-        <v>8.667733439449027</v>
+        <v>8.175508481680012</v>
       </c>
       <c r="D10" t="n">
-        <v>6.791072361364965</v>
+        <v>6.337735752523598</v>
       </c>
       <c r="E10" t="n">
-        <v>17.3242661335234</v>
+        <v>16.36190915662754</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.177654430072039</v>
+        <v>2.177935169608417</v>
       </c>
       <c r="C11" t="n">
-        <v>10.4242519845532</v>
+        <v>9.795595734776013</v>
       </c>
       <c r="D11" t="n">
-        <v>7.264540889718717</v>
+        <v>6.870692453721582</v>
       </c>
       <c r="E11" t="n">
-        <v>19.86644730434395</v>
+        <v>18.84422335810601</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.469595766564989</v>
+        <v>2.509239571659954</v>
       </c>
       <c r="C12" t="n">
-        <v>12.24736248909871</v>
+        <v>11.4702953597623</v>
       </c>
       <c r="D12" t="n">
-        <v>7.677702246690798</v>
+        <v>7.272009497820474</v>
       </c>
       <c r="E12" t="n">
-        <v>22.39466050235449</v>
+        <v>21.25154442924273</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.747384616149802</v>
+        <v>2.828655257974106</v>
       </c>
       <c r="C13" t="n">
-        <v>14.09415693658704</v>
+        <v>13.20806176455118</v>
       </c>
       <c r="D13" t="n">
-        <v>8.06646005052019</v>
+        <v>7.735806263583168</v>
       </c>
       <c r="E13" t="n">
-        <v>24.90800160325703</v>
+        <v>23.77252328610845</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.57653955086474</v>
+        <v>1.628542726758694</v>
       </c>
       <c r="C14" t="n">
-        <v>9.764374309145394</v>
+        <v>9.20376691758934</v>
       </c>
       <c r="D14" t="n">
-        <v>6.088465467519274</v>
+        <v>5.876525773126473</v>
       </c>
       <c r="E14" t="n">
-        <v>17.42937932752941</v>
+        <v>16.70883541747451</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.60275221456813</v>
+        <v>1.670345544005523</v>
       </c>
       <c r="C15" t="n">
-        <v>10.67299162690286</v>
+        <v>10.01476906111354</v>
       </c>
       <c r="D15" t="n">
-        <v>6.045307838440584</v>
+        <v>5.856615929684348</v>
       </c>
       <c r="E15" t="n">
-        <v>18.32105167991157</v>
+        <v>17.54173053480341</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.836329628362531</v>
+        <v>1.929232413615407</v>
       </c>
       <c r="C16" t="n">
-        <v>12.72283174598499</v>
+        <v>11.90204157784944</v>
       </c>
       <c r="D16" t="n">
-        <v>6.444967511362418</v>
+        <v>6.228295793035147</v>
       </c>
       <c r="E16" t="n">
-        <v>21.00412888570994</v>
+        <v>20.0595697845</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.457541911632985</v>
+        <v>1.543169946397392</v>
       </c>
       <c r="C17" t="n">
-        <v>11.80526088916479</v>
+        <v>11.01679967293009</v>
       </c>
       <c r="D17" t="n">
-        <v>5.93435071290661</v>
+        <v>5.736842709766236</v>
       </c>
       <c r="E17" t="n">
-        <v>19.19715351370439</v>
+        <v>18.29681232909372</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.642159567416597</v>
+        <v>1.754883838818216</v>
       </c>
       <c r="C18" t="n">
-        <v>13.88089152043748</v>
+        <v>12.88843294873734</v>
       </c>
       <c r="D18" t="n">
-        <v>6.308583120288452</v>
+        <v>6.074632642366437</v>
       </c>
       <c r="E18" t="n">
-        <v>21.83163420814253</v>
+        <v>20.71794942992199</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.626667588643583</v>
+        <v>1.754078805700734</v>
       </c>
       <c r="C19" t="n">
-        <v>14.90988092421265</v>
+        <v>13.81789277025597</v>
       </c>
       <c r="D19" t="n">
-        <v>6.343837680347955</v>
+        <v>6.129119639952134</v>
       </c>
       <c r="E19" t="n">
-        <v>22.88038619320419</v>
+        <v>21.70109121590884</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.793073824513417</v>
+        <v>1.948072152059904</v>
       </c>
       <c r="C20" t="n">
-        <v>17.09292457180699</v>
+        <v>15.84425930172955</v>
       </c>
       <c r="D20" t="n">
-        <v>6.736605484385976</v>
+        <v>6.50217395008888</v>
       </c>
       <c r="E20" t="n">
-        <v>25.62260388070638</v>
+        <v>24.29450540387833</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.056880856052819</v>
+        <v>1.154672744872844</v>
       </c>
       <c r="C21" t="n">
-        <v>12.52338969986725</v>
+        <v>11.61017780285391</v>
       </c>
       <c r="D21" t="n">
-        <v>5.583228646482739</v>
+        <v>5.398689530515465</v>
       </c>
       <c r="E21" t="n">
-        <v>19.16349920240281</v>
+        <v>18.16354007824222</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_34_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249447168521912</v>
+        <v>2.600315396213886</v>
       </c>
       <c r="C3" t="n">
-        <v>4.612502914771668</v>
+        <v>7.65604864867779</v>
       </c>
       <c r="D3" t="n">
-        <v>6.047345058861536</v>
+        <v>8.231117819618316</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90929514215512</v>
+        <v>18.48748186450999</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.368716829038843</v>
+        <v>1.09577897188357</v>
       </c>
       <c r="C4" t="n">
-        <v>5.114406160457275</v>
+        <v>4.353213293823212</v>
       </c>
       <c r="D4" t="n">
-        <v>6.315098865898177</v>
+        <v>5.918034150847927</v>
       </c>
       <c r="E4" t="n">
-        <v>12.79822185539429</v>
+        <v>11.36702641655471</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.536481830313446</v>
+        <v>1.21144971156027</v>
       </c>
       <c r="C5" t="n">
-        <v>5.765294240591599</v>
+        <v>4.800427147455149</v>
       </c>
       <c r="D5" t="n">
-        <v>6.626333007151276</v>
+        <v>6.252232828319555</v>
       </c>
       <c r="E5" t="n">
-        <v>13.92810907805632</v>
+        <v>12.26410968733497</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.735580846326422</v>
+        <v>1.334980281438484</v>
       </c>
       <c r="C6" t="n">
-        <v>6.594201618341576</v>
+        <v>5.34847386374865</v>
       </c>
       <c r="D6" t="n">
-        <v>6.922626489598771</v>
+        <v>6.668881214121962</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25240895426677</v>
+        <v>13.3523353593091</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.961589285319592</v>
+        <v>1.462590903672805</v>
       </c>
       <c r="C7" t="n">
-        <v>7.607377649546716</v>
+        <v>6.041592870369229</v>
       </c>
       <c r="D7" t="n">
-        <v>7.306787137193674</v>
+        <v>7.050947222759635</v>
       </c>
       <c r="E7" t="n">
-        <v>16.87575407205998</v>
+        <v>14.55513099680167</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.208833694622786</v>
+        <v>1.595388021236813</v>
       </c>
       <c r="C8" t="n">
-        <v>5.36156005079474</v>
+        <v>6.865460014772196</v>
       </c>
       <c r="D8" t="n">
-        <v>5.502998670771673</v>
+        <v>7.513930955897889</v>
       </c>
       <c r="E8" t="n">
-        <v>12.0733924161892</v>
+        <v>15.9747789919069</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.523677798880383</v>
+        <v>1.751380529326242</v>
       </c>
       <c r="C9" t="n">
-        <v>6.691612393393815</v>
+        <v>7.860511936717405</v>
       </c>
       <c r="D9" t="n">
-        <v>5.943081914465901</v>
+        <v>8.018245291944814</v>
       </c>
       <c r="E9" t="n">
-        <v>14.1583721067401</v>
+        <v>17.63013775798846</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.848664922423929</v>
+        <v>1.098791665547115</v>
       </c>
       <c r="C10" t="n">
-        <v>8.175508481680012</v>
+        <v>6.049961322558715</v>
       </c>
       <c r="D10" t="n">
-        <v>6.337735752523598</v>
+        <v>6.315720426098325</v>
       </c>
       <c r="E10" t="n">
-        <v>16.36190915662754</v>
+        <v>13.46447341420416</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.177935169608417</v>
+        <v>1.051225989276357</v>
       </c>
       <c r="C11" t="n">
-        <v>9.795595734776013</v>
+        <v>6.336180048254829</v>
       </c>
       <c r="D11" t="n">
-        <v>6.870692453721582</v>
+        <v>6.232134426558752</v>
       </c>
       <c r="E11" t="n">
-        <v>18.84422335810601</v>
+        <v>13.61954046408994</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.509239571659954</v>
+        <v>1.159610935825205</v>
       </c>
       <c r="C12" t="n">
-        <v>11.4702953597623</v>
+        <v>7.474997567704087</v>
       </c>
       <c r="D12" t="n">
-        <v>7.272009497820474</v>
+        <v>6.725531370282071</v>
       </c>
       <c r="E12" t="n">
-        <v>21.25154442924273</v>
+        <v>15.36013987381136</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.828655257974106</v>
+        <v>0.9318061985317753</v>
       </c>
       <c r="C13" t="n">
-        <v>13.20806176455118</v>
+        <v>7.158403568038576</v>
       </c>
       <c r="D13" t="n">
-        <v>7.735806263583168</v>
+        <v>6.204341149051526</v>
       </c>
       <c r="E13" t="n">
-        <v>23.77252328610845</v>
+        <v>14.29455091562188</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.628542726758694</v>
+        <v>1.029568634920673</v>
       </c>
       <c r="C14" t="n">
-        <v>9.20376691758934</v>
+        <v>8.42123545748829</v>
       </c>
       <c r="D14" t="n">
-        <v>5.876525773126473</v>
+        <v>6.629398635082223</v>
       </c>
       <c r="E14" t="n">
-        <v>16.70883541747451</v>
+        <v>16.08020272749119</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.670345544005523</v>
+        <v>1.014793331971758</v>
       </c>
       <c r="C15" t="n">
-        <v>10.01476906111354</v>
+        <v>9.157300798747336</v>
       </c>
       <c r="D15" t="n">
-        <v>5.856615929684348</v>
+        <v>6.729870695134843</v>
       </c>
       <c r="E15" t="n">
-        <v>17.54173053480341</v>
+        <v>16.90196482585394</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.929232413615407</v>
+        <v>1.126928554750829</v>
       </c>
       <c r="C16" t="n">
-        <v>11.90204157784944</v>
+        <v>10.77841169538488</v>
       </c>
       <c r="D16" t="n">
-        <v>6.228295793035147</v>
+        <v>7.256205274335643</v>
       </c>
       <c r="E16" t="n">
-        <v>20.0595697845</v>
+        <v>19.16154552447135</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.543169946397392</v>
+        <v>0.6836891012374788</v>
       </c>
       <c r="C17" t="n">
-        <v>11.01679967293009</v>
+        <v>8.204661913931444</v>
       </c>
       <c r="D17" t="n">
-        <v>5.736842709766236</v>
+        <v>6.075781287180406</v>
       </c>
       <c r="E17" t="n">
-        <v>18.29681232909372</v>
+        <v>14.96413230234933</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.754883838818216</v>
+        <v>0.5494940075439823</v>
       </c>
       <c r="C18" t="n">
-        <v>12.88843294873734</v>
+        <v>7.3560391983805</v>
       </c>
       <c r="D18" t="n">
-        <v>6.074632642366437</v>
+        <v>5.577318525303173</v>
       </c>
       <c r="E18" t="n">
-        <v>20.71794942992199</v>
+        <v>13.48285173122765</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.754078805700734</v>
+        <v>0.6498286229180062</v>
       </c>
       <c r="C19" t="n">
-        <v>13.81789277025597</v>
+        <v>9.192987327796708</v>
       </c>
       <c r="D19" t="n">
-        <v>6.129119639952134</v>
+        <v>6.206196652212552</v>
       </c>
       <c r="E19" t="n">
-        <v>21.70109121590884</v>
+        <v>16.04901260292727</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.948072152059904</v>
+        <v>0.7456570163295375</v>
       </c>
       <c r="C20" t="n">
-        <v>15.84425930172955</v>
+        <v>11.18312736898359</v>
       </c>
       <c r="D20" t="n">
-        <v>6.50217395008888</v>
+        <v>6.815047125955297</v>
       </c>
       <c r="E20" t="n">
-        <v>24.29450540387833</v>
+        <v>18.74383151126842</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.154672744872844</v>
+        <v>0.8302149460963152</v>
       </c>
       <c r="C21" t="n">
-        <v>11.61017780285391</v>
+        <v>13.16998837283828</v>
       </c>
       <c r="D21" t="n">
-        <v>5.398689530515465</v>
+        <v>7.384558969188872</v>
       </c>
       <c r="E21" t="n">
-        <v>18.16354007824222</v>
+        <v>21.38476228812347</v>
       </c>
     </row>
   </sheetData>
